--- a/SCENARIOS/SCENARIO 2/Simulation Results/Scenario_2_Benchmarking_100.xlsx
+++ b/SCENARIOS/SCENARIO 2/Simulation Results/Scenario_2_Benchmarking_100.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="9">
   <si>
     <t>Run</t>
   </si>
@@ -39,6 +39,9 @@
     <t>SimulationTime_s</t>
   </si>
   <si>
+    <t>Total TL</t>
+  </si>
+  <si>
     <t>Number of runs</t>
   </si>
   <si>
@@ -46,6 +49,9 @@
   </si>
   <si>
     <t>Average simulation time (s)</t>
+  </si>
+  <si>
+    <t>Average Total TL (sum toxic load accumulated)</t>
   </si>
 </sst>
 </file>
@@ -397,10 +403,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CAF0E20E-E4D8-9B45-9C94-E89B574F109C}">
-  <dimension ref="A1:D54"/>
+  <dimension ref="A1:E55"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:4">
+    <row r="1" spans="1:5">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -413,729 +419,890 @@
       <c r="D1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="2" spans="1:4">
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
       <c r="A2">
         <v>1.0</v>
       </c>
       <c r="B2">
-        <v>3.393921676e9</v>
+        <v>1.767061827e9</v>
       </c>
       <c r="C2">
-        <v>126.17181030000008</v>
+        <v>116.39624289999996</v>
       </c>
       <c r="D2">
-        <v>3.3103885</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4">
+        <v>1.949549</v>
+      </c>
+      <c r="E2">
+        <v>25.680000000000014</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5">
       <c r="A3">
         <v>2.0</v>
       </c>
       <c r="B3">
-        <v>2.263385677e9</v>
+        <v>2.699867572e9</v>
       </c>
       <c r="C3">
-        <v>119.98733629999998</v>
+        <v>114.95976119999996</v>
       </c>
       <c r="D3">
-        <v>0.1709623</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4">
+        <v>0.1164343</v>
+      </c>
+      <c r="E3">
+        <v>38.98000000000001</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5">
       <c r="A4">
         <v>3.0</v>
       </c>
       <c r="B4">
-        <v>1.030603688e9</v>
+        <v>1.42106317e9</v>
       </c>
       <c r="C4">
-        <v>111.56578800000003</v>
+        <v>118.21686030000001</v>
       </c>
       <c r="D4">
-        <v>0.134135</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4">
+        <v>0.1221395</v>
+      </c>
+      <c r="E4">
+        <v>23.960000000000008</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5">
       <c r="A5">
         <v>4.0</v>
       </c>
       <c r="B5">
-        <v>3.448052043e9</v>
+        <v>3.314581806e9</v>
       </c>
       <c r="C5">
-        <v>114.10630599999999</v>
+        <v>107.83338170000002</v>
       </c>
       <c r="D5">
-        <v>0.1365477</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4">
+        <v>0.1228586</v>
+      </c>
+      <c r="E5">
+        <v>32.59000000000001</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5">
       <c r="A6">
         <v>5.0</v>
       </c>
       <c r="B6">
-        <v>1.947115657e9</v>
+        <v>2.462618083e9</v>
       </c>
       <c r="C6">
-        <v>141.15740119999995</v>
+        <v>107.7533546</v>
       </c>
       <c r="D6">
-        <v>0.2151951</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4">
+        <v>0.1465717</v>
+      </c>
+      <c r="E6">
+        <v>28.610000000000007</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5">
       <c r="A7">
         <v>6.0</v>
       </c>
       <c r="B7">
-        <v>1.119852308e9</v>
+        <v>1.218934086e9</v>
       </c>
       <c r="C7">
-        <v>111.12877210000002</v>
+        <v>105.58073959999999</v>
       </c>
       <c r="D7">
-        <v>0.3357938</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4">
+        <v>0.1618547</v>
+      </c>
+      <c r="E7">
+        <v>28.480000000000015</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5">
       <c r="A8">
         <v>7.0</v>
       </c>
       <c r="B8">
-        <v>3.17072913e9</v>
+        <v>3.973755835e9</v>
       </c>
       <c r="C8">
-        <v>111.61299610000003</v>
+        <v>105.46664230000005</v>
       </c>
       <c r="D8">
-        <v>0.2105665</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4">
+        <v>0.2415977</v>
+      </c>
+      <c r="E8">
+        <v>26.19000000000001</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5">
       <c r="A9">
         <v>8.0</v>
       </c>
       <c r="B9">
-        <v>1.14532146e8</v>
+        <v>3.820596653e9</v>
       </c>
       <c r="C9">
-        <v>111.13348080000006</v>
+        <v>108.95116499999997</v>
       </c>
       <c r="D9">
-        <v>0.7100882</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4">
+        <v>0.2101183</v>
+      </c>
+      <c r="E9">
+        <v>30.390000000000015</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5">
       <c r="A10">
         <v>9.0</v>
       </c>
       <c r="B10">
-        <v>1.522384389e9</v>
+        <v>5.17388888e8</v>
       </c>
       <c r="C10">
-        <v>111.59308240000003</v>
+        <v>110.3468974</v>
       </c>
       <c r="D10">
-        <v>0.2110006</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4">
+        <v>0.2038605</v>
+      </c>
+      <c r="E10">
+        <v>18.020000000000007</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5">
       <c r="A11">
         <v>10.0</v>
       </c>
       <c r="B11">
-        <v>3.66161022e8</v>
+        <v>8.88462956e8</v>
       </c>
       <c r="C11">
-        <v>113.4233003999999</v>
+        <v>104.37668130000006</v>
       </c>
       <c r="D11">
-        <v>0.3164785</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4">
+        <v>0.2072586</v>
+      </c>
+      <c r="E11">
+        <v>24.265000000000008</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5">
       <c r="A12">
         <v>11.0</v>
       </c>
       <c r="B12">
-        <v>2.2915844e7</v>
+        <v>1.03117194e8</v>
       </c>
       <c r="C12">
-        <v>111.55523210000001</v>
+        <v>102.5025658</v>
       </c>
       <c r="D12">
-        <v>0.2313863</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4">
+        <v>0.3341895</v>
+      </c>
+      <c r="E12">
+        <v>26.11000000000001</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5">
       <c r="A13">
         <v>12.0</v>
       </c>
       <c r="B13">
-        <v>2.439062705e9</v>
+        <v>1.817983995e9</v>
       </c>
       <c r="C13">
-        <v>113.2841179</v>
+        <v>125.04177569999997</v>
       </c>
       <c r="D13">
-        <v>0.3104595</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4">
+        <v>0.3863212</v>
+      </c>
+      <c r="E13">
+        <v>29.88000000000001</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5">
       <c r="A14">
         <v>13.0</v>
       </c>
       <c r="B14">
-        <v>3.864544961e9</v>
+        <v>2.718850466e9</v>
       </c>
       <c r="C14">
-        <v>110.17292510000001</v>
+        <v>126.88559000000001</v>
       </c>
       <c r="D14">
-        <v>0.3341948</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4">
+        <v>0.7578821</v>
+      </c>
+      <c r="E14">
+        <v>22.13500000000001</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5">
       <c r="A15">
         <v>14.0</v>
       </c>
       <c r="B15">
-        <v>1.31623875e9</v>
+        <v>1.168807909e9</v>
       </c>
       <c r="C15">
-        <v>115.47537600000003</v>
+        <v>146.12220149999996</v>
       </c>
       <c r="D15">
-        <v>0.280006</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4">
+        <v>0.3188564</v>
+      </c>
+      <c r="E15">
+        <v>40.63500000000002</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5">
       <c r="A16">
         <v>15.0</v>
       </c>
       <c r="B16">
-        <v>1.190110125e9</v>
+        <v>3.321116878e9</v>
       </c>
       <c r="C16">
-        <v>110.82161509999997</v>
+        <v>151.8967067</v>
       </c>
       <c r="D16">
-        <v>0.3363389</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4">
+        <v>0.496196</v>
+      </c>
+      <c r="E16">
+        <v>37.35500000000002</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
       <c r="A17">
         <v>16.0</v>
       </c>
       <c r="B17">
-        <v>3.168525329e9</v>
+        <v>2.195679617e9</v>
       </c>
       <c r="C17">
-        <v>112.52883699999997</v>
+        <v>128.54059569999998</v>
       </c>
       <c r="D17">
-        <v>0.2685425</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4">
+        <v>0.2339161</v>
+      </c>
+      <c r="E17">
+        <v>23.175000000000008</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
       <c r="A18">
         <v>17.0</v>
       </c>
       <c r="B18">
-        <v>4.105570977e9</v>
+        <v>3.99206765e9</v>
       </c>
       <c r="C18">
-        <v>115.39101429999995</v>
+        <v>103.74967779999996</v>
       </c>
       <c r="D18">
-        <v>0.85134</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4">
+        <v>0.316329</v>
+      </c>
+      <c r="E18">
+        <v>44.405000000000015</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
       <c r="A19">
         <v>18.0</v>
       </c>
       <c r="B19">
-        <v>2.81582615e9</v>
+        <v>1.98751265e8</v>
       </c>
       <c r="C19">
-        <v>110.18686819999995</v>
+        <v>107.16456639999998</v>
       </c>
       <c r="D19">
-        <v>0.9031037</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4">
+        <v>0.7841953</v>
+      </c>
+      <c r="E19">
+        <v>25.125000000000004</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
       <c r="A20">
         <v>19.0</v>
       </c>
       <c r="B20">
-        <v>1.463772931e9</v>
+        <v>1.59205242e8</v>
       </c>
       <c r="C20">
-        <v>112.76179640000001</v>
+        <v>103.92234530000002</v>
       </c>
       <c r="D20">
-        <v>0.8533967</v>
-      </c>
-    </row>
-    <row r="21" spans="1:4">
+        <v>0.2922496</v>
+      </c>
+      <c r="E20">
+        <v>35.83000000000001</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
       <c r="A21">
         <v>20.0</v>
       </c>
       <c r="B21">
-        <v>1.309820488e9</v>
+        <v>4.275543679e9</v>
       </c>
       <c r="C21">
-        <v>112.07702380000005</v>
+        <v>113.39342279999995</v>
       </c>
       <c r="D21">
-        <v>0.3588973</v>
-      </c>
-    </row>
-    <row r="22" spans="1:4">
+        <v>0.3885224</v>
+      </c>
+      <c r="E21">
+        <v>48.16500000000001</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
       <c r="A22">
         <v>21.0</v>
       </c>
       <c r="B22">
-        <v>4.030887715e9</v>
+        <v>1.285197131e9</v>
       </c>
       <c r="C22">
-        <v>108.39094010000002</v>
+        <v>107.53677779999998</v>
       </c>
       <c r="D22">
-        <v>0.4080869</v>
-      </c>
-    </row>
-    <row r="23" spans="1:4">
+        <v>0.8373444</v>
+      </c>
+      <c r="E22">
+        <v>31.415000000000013</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
       <c r="A23">
         <v>22.0</v>
       </c>
       <c r="B23">
-        <v>1.753137472e9</v>
+        <v>2.943423022e9</v>
       </c>
       <c r="C23">
-        <v>112.15208729999999</v>
+        <v>104.44872209999998</v>
       </c>
       <c r="D23">
-        <v>1.1187024</v>
-      </c>
-    </row>
-    <row r="24" spans="1:4">
+        <v>0.3704452</v>
+      </c>
+      <c r="E23">
+        <v>29.73500000000001</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
       <c r="A24">
         <v>23.0</v>
       </c>
       <c r="B24">
-        <v>2.958890047e9</v>
+        <v>1.688096789e9</v>
       </c>
       <c r="C24">
-        <v>111.95140339999995</v>
+        <v>102.8798203</v>
       </c>
       <c r="D24">
-        <v>1.024971</v>
-      </c>
-    </row>
-    <row r="25" spans="1:4">
+        <v>0.3839477</v>
+      </c>
+      <c r="E24">
+        <v>30.45000000000001</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
       <c r="A25">
         <v>24.0</v>
       </c>
       <c r="B25">
-        <v>2.281968278e9</v>
+        <v>2.348261026e9</v>
       </c>
       <c r="C25">
-        <v>113.68610139999998</v>
+        <v>106.48967949999998</v>
       </c>
       <c r="D25">
-        <v>0.3925702</v>
-      </c>
-    </row>
-    <row r="26" spans="1:4">
+        <v>0.367816</v>
+      </c>
+      <c r="E25">
+        <v>30.865000000000013</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
       <c r="A26">
         <v>25.0</v>
       </c>
       <c r="B26">
-        <v>7.19599373e8</v>
+        <v>2.13689952e9</v>
       </c>
       <c r="C26">
-        <v>111.08306900000002</v>
+        <v>108.45489439999999</v>
       </c>
       <c r="D26">
-        <v>0.3717349</v>
-      </c>
-    </row>
-    <row r="27" spans="1:4">
+        <v>0.4624792</v>
+      </c>
+      <c r="E26">
+        <v>32.805000000000014</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
       <c r="A27">
         <v>26.0</v>
       </c>
       <c r="B27">
-        <v>3.852357414e9</v>
+        <v>8.04369189e8</v>
       </c>
       <c r="C27">
-        <v>113.07724730000007</v>
+        <v>103.96651300000002</v>
       </c>
       <c r="D27">
-        <v>0.9567991</v>
-      </c>
-    </row>
-    <row r="28" spans="1:4">
+        <v>0.4399072</v>
+      </c>
+      <c r="E27">
+        <v>36.065000000000005</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
       <c r="A28">
         <v>27.0</v>
       </c>
       <c r="B28">
-        <v>2.166639782e9</v>
+        <v>2.276530478e9</v>
       </c>
       <c r="C28">
-        <v>106.37129649999996</v>
+        <v>103.04764850000002</v>
       </c>
       <c r="D28">
-        <v>0.4522875</v>
-      </c>
-    </row>
-    <row r="29" spans="1:4">
+        <v>0.3978272</v>
+      </c>
+      <c r="E28">
+        <v>30.81500000000001</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
       <c r="A29">
         <v>28.0</v>
       </c>
       <c r="B29">
-        <v>3.155051586e9</v>
+        <v>3.480333651e9</v>
       </c>
       <c r="C29">
-        <v>114.08963989999998</v>
+        <v>107.63897139999999</v>
       </c>
       <c r="D29">
-        <v>1.1096708</v>
-      </c>
-    </row>
-    <row r="30" spans="1:4">
+        <v>0.865317</v>
+      </c>
+      <c r="E29">
+        <v>35.165000000000006</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5">
       <c r="A30">
         <v>29.0</v>
       </c>
       <c r="B30">
-        <v>3.686337e9</v>
+        <v>4.093730061e9</v>
       </c>
       <c r="C30">
-        <v>112.67152890000001</v>
+        <v>110.2422078</v>
       </c>
       <c r="D30">
-        <v>1.0837543</v>
-      </c>
-    </row>
-    <row r="31" spans="1:4">
+        <v>0.5056358</v>
+      </c>
+      <c r="E30">
+        <v>20.255000000000003</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5">
       <c r="A31">
         <v>30.0</v>
       </c>
       <c r="B31">
-        <v>2.252476626e9</v>
+        <v>1.402872678e9</v>
       </c>
       <c r="C31">
-        <v>111.66498299999999</v>
+        <v>113.86565099999999</v>
       </c>
       <c r="D31">
-        <v>1.0226152</v>
-      </c>
-    </row>
-    <row r="32" spans="1:4">
+        <v>0.540995</v>
+      </c>
+      <c r="E31">
+        <v>28.105000000000015</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5">
       <c r="A32">
         <v>31.0</v>
       </c>
       <c r="B32">
-        <v>1.68579083e9</v>
+        <v>1.393938345e9</v>
       </c>
       <c r="C32">
-        <v>114.12015939999999</v>
+        <v>106.3607767</v>
       </c>
       <c r="D32">
-        <v>0.450148</v>
-      </c>
-    </row>
-    <row r="33" spans="1:4">
+        <v>0.428527</v>
+      </c>
+      <c r="E32">
+        <v>32.13000000000001</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5">
       <c r="A33">
         <v>32.0</v>
       </c>
       <c r="B33">
-        <v>3.260977229e9</v>
+        <v>2.590949001e9</v>
       </c>
       <c r="C33">
-        <v>112.51152349999998</v>
+        <v>126.29832020000006</v>
       </c>
       <c r="D33">
-        <v>0.5076888</v>
-      </c>
-    </row>
-    <row r="34" spans="1:4">
+        <v>1.0074753</v>
+      </c>
+      <c r="E33">
+        <v>33.22000000000001</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5">
       <c r="A34">
         <v>33.0</v>
       </c>
       <c r="B34">
-        <v>2.464021001e9</v>
+        <v>1.433724117e9</v>
       </c>
       <c r="C34">
-        <v>109.65662689999999</v>
+        <v>145.8085097</v>
       </c>
       <c r="D34">
-        <v>1.1566442</v>
-      </c>
-    </row>
-    <row r="35" spans="1:4">
+        <v>1.3192672</v>
+      </c>
+      <c r="E34">
+        <v>40.510000000000005</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5">
       <c r="A35">
         <v>34.0</v>
       </c>
       <c r="B35">
-        <v>3.218484724e9</v>
+        <v>1.29646057e9</v>
       </c>
       <c r="C35">
-        <v>110.34570449999998</v>
+        <v>166.43433170000003</v>
       </c>
       <c r="D35">
-        <v>1.1471079</v>
-      </c>
-    </row>
-    <row r="36" spans="1:4">
+        <v>1.2755667</v>
+      </c>
+      <c r="E35">
+        <v>41.30500000000002</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5">
       <c r="A36">
         <v>35.0</v>
       </c>
       <c r="B36">
-        <v>1.914321025e9</v>
+        <v>3.169800487e9</v>
       </c>
       <c r="C36">
-        <v>110.265146</v>
+        <v>158.81093019999992</v>
       </c>
       <c r="D36">
-        <v>0.4424137</v>
-      </c>
-    </row>
-    <row r="37" spans="1:4">
+        <v>1.2308949</v>
+      </c>
+      <c r="E36">
+        <v>37.66500000000003</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5">
       <c r="A37">
         <v>36.0</v>
       </c>
       <c r="B37">
-        <v>1.337789336e9</v>
+        <v>2.968182726e9</v>
       </c>
       <c r="C37">
-        <v>109.62130099999996</v>
+        <v>100.30153279999999</v>
       </c>
       <c r="D37">
-        <v>1.0015488</v>
-      </c>
-    </row>
-    <row r="38" spans="1:4">
+        <v>0.5057055</v>
+      </c>
+      <c r="E37">
+        <v>23.520000000000007</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5">
       <c r="A38">
         <v>37.0</v>
       </c>
       <c r="B38">
-        <v>3.91925869e8</v>
+        <v>4.228450247e9</v>
       </c>
       <c r="C38">
-        <v>112.4114228</v>
+        <v>103.69974620000004</v>
       </c>
       <c r="D38">
-        <v>0.7682202</v>
-      </c>
-    </row>
-    <row r="39" spans="1:4">
+        <v>0.5793155</v>
+      </c>
+      <c r="E38">
+        <v>32.70000000000002</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5">
       <c r="A39">
         <v>38.0</v>
       </c>
       <c r="B39">
-        <v>1.461992687e9</v>
+        <v>3.829622837e9</v>
       </c>
       <c r="C39">
-        <v>109.00690060000002</v>
+        <v>109.0547837</v>
       </c>
       <c r="D39">
-        <v>0.5578379</v>
-      </c>
-    </row>
-    <row r="40" spans="1:4">
+        <v>1.0575021</v>
+      </c>
+      <c r="E39">
+        <v>30.140000000000015</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5">
       <c r="A40">
         <v>39.0</v>
       </c>
       <c r="B40">
-        <v>1.767545552e9</v>
+        <v>4.288661716e9</v>
       </c>
       <c r="C40">
-        <v>113.509895</v>
+        <v>103.56356919999999</v>
       </c>
       <c r="D40">
-        <v>0.5705401</v>
-      </c>
-    </row>
-    <row r="41" spans="1:4">
+        <v>0.5895706</v>
+      </c>
+      <c r="E40">
+        <v>36.02500000000001</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5">
       <c r="A41">
         <v>40.0</v>
       </c>
       <c r="B41">
-        <v>3.403795972e9</v>
+        <v>3.443409684e9</v>
       </c>
       <c r="C41">
-        <v>114.30632680000001</v>
+        <v>102.77742420000004</v>
       </c>
       <c r="D41">
-        <v>1.2101212</v>
-      </c>
-    </row>
-    <row r="42" spans="1:4">
+        <v>0.9896967</v>
+      </c>
+      <c r="E41">
+        <v>34.475000000000016</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5">
       <c r="A42">
         <v>41.0</v>
       </c>
       <c r="B42">
-        <v>1.063004689e9</v>
+        <v>2.443600534e9</v>
       </c>
       <c r="C42">
-        <v>109.69726590000002</v>
+        <v>104.88856259999997</v>
       </c>
       <c r="D42">
-        <v>0.5988552</v>
-      </c>
-    </row>
-    <row r="43" spans="1:4">
+        <v>0.6195448</v>
+      </c>
+      <c r="E42">
+        <v>33.06000000000001</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5">
       <c r="A43">
         <v>42.0</v>
       </c>
       <c r="B43">
-        <v>3.193416145e9</v>
+        <v>1.429511034e9</v>
       </c>
       <c r="C43">
-        <v>120.35718690000002</v>
+        <v>105.08218610000004</v>
       </c>
       <c r="D43">
-        <v>1.2196277</v>
-      </c>
-    </row>
-    <row r="44" spans="1:4">
+        <v>0.9901701</v>
+      </c>
+      <c r="E43">
+        <v>29.105000000000015</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5">
       <c r="A44">
         <v>43.0</v>
       </c>
       <c r="B44">
-        <v>3.021006618e9</v>
+        <v>4.245992511e9</v>
       </c>
       <c r="C44">
-        <v>113.64187919999998</v>
+        <v>105.56671820000001</v>
       </c>
       <c r="D44">
-        <v>1.2919175</v>
-      </c>
-    </row>
-    <row r="45" spans="1:4">
+        <v>1.0496881</v>
+      </c>
+      <c r="E44">
+        <v>34.53500000000002</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5">
       <c r="A45">
         <v>44.0</v>
       </c>
       <c r="B45">
-        <v>1.867962302e9</v>
+        <v>4.212120141e9</v>
       </c>
       <c r="C45">
-        <v>113.37269449999997</v>
+        <v>103.08916640000001</v>
       </c>
       <c r="D45">
-        <v>1.3236611</v>
-      </c>
-    </row>
-    <row r="46" spans="1:4">
+        <v>0.6000327</v>
+      </c>
+      <c r="E45">
+        <v>22.92000000000001</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5">
       <c r="A46">
         <v>45.0</v>
       </c>
       <c r="B46">
-        <v>3.343265719e9</v>
+        <v>1.605732011e9</v>
       </c>
       <c r="C46">
-        <v>116.41962790000001</v>
+        <v>106.53194649999998</v>
       </c>
       <c r="D46">
-        <v>1.4105609</v>
-      </c>
-    </row>
-    <row r="47" spans="1:4">
+        <v>1.1231068</v>
+      </c>
+      <c r="E46">
+        <v>46.640000000000015</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5">
       <c r="A47">
         <v>46.0</v>
       </c>
       <c r="B47">
-        <v>1.08538e7</v>
+        <v>3.074745626e9</v>
       </c>
       <c r="C47">
-        <v>113.86415499999998</v>
+        <v>104.8572742</v>
       </c>
       <c r="D47">
-        <v>1.6421192</v>
-      </c>
-    </row>
-    <row r="48" spans="1:4">
+        <v>0.6925398</v>
+      </c>
+      <c r="E47">
+        <v>24.705000000000016</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5">
       <c r="A48">
         <v>47.0</v>
       </c>
       <c r="B48">
-        <v>3.165499708e9</v>
+        <v>3.218128527e9</v>
       </c>
       <c r="C48">
-        <v>115.74859349999997</v>
+        <v>106.80420310000004</v>
       </c>
       <c r="D48">
-        <v>1.2033867</v>
-      </c>
-    </row>
-    <row r="49" spans="1:4">
+        <v>1.1719803</v>
+      </c>
+      <c r="E48">
+        <v>45.33000000000001</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5">
       <c r="A49">
         <v>48.0</v>
       </c>
       <c r="B49">
-        <v>1.88742897e9</v>
+        <v>8.06067246e8</v>
       </c>
       <c r="C49">
-        <v>117.15356460000001</v>
+        <v>107.07832769999996</v>
       </c>
       <c r="D49">
-        <v>1.5163661</v>
-      </c>
-    </row>
-    <row r="50" spans="1:4">
+        <v>1.1457534</v>
+      </c>
+      <c r="E49">
+        <v>36.16500000000001</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5">
       <c r="A50">
         <v>49.0</v>
       </c>
       <c r="B50">
-        <v>1.21156798e8</v>
+        <v>4.131202238e9</v>
       </c>
       <c r="C50">
-        <v>111.50654229999998</v>
+        <v>104.74634230000001</v>
       </c>
       <c r="D50">
-        <v>0.8987294</v>
-      </c>
-    </row>
-    <row r="51" spans="1:4">
+        <v>0.718981</v>
+      </c>
+      <c r="E50">
+        <v>25.545000000000012</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5">
       <c r="A51">
         <v>50.0</v>
       </c>
       <c r="B51">
-        <v>3.963510789e9</v>
+        <v>4.58290507e8</v>
       </c>
       <c r="C51">
-        <v>113.05700040000002</v>
+        <v>104.14141110000001</v>
       </c>
       <c r="D51">
-        <v>0.7143093</v>
-      </c>
-    </row>
-    <row r="52" spans="1:4">
+        <v>1.0622507</v>
+      </c>
+      <c r="E51">
+        <v>29.50000000000001</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5">
       <c r="A52" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B52">
         <v>50</v>
       </c>
     </row>
-    <row r="53" spans="1:4">
+    <row r="53" spans="1:5">
       <c r="A53" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B53">
-        <v>113.43693786</v>
-      </c>
-    </row>
-    <row r="54" spans="1:4">
+        <v>113.07136245199999</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5">
       <c r="A54" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B54">
-        <v>0.7610363620000001</v>
+        <v>0.622403688</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5">
+      <c r="A55" t="s">
+        <v>8</v>
+      </c>
+      <c r="B55">
+        <v>31.697000000000017</v>
       </c>
     </row>
   </sheetData>
